--- a/data/trans_camb/IP1013-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/IP1013-Provincia-trans_camb.xlsx
@@ -583,7 +583,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -739,7 +739,7 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -895,7 +895,7 @@
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -943,7 +943,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,42</t>
+          <t>0,0; 5,4</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,65</t>
+          <t>0,0; 2,46</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1109,22 +1109,22 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-2,6; 1,72</t>
+          <t>-2,58; 1,67</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-4,61; 0,0</t>
+          <t>-4,27; 0,0</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-1,32; 0,86</t>
+          <t>-1,73; 0,85</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-2,18; 0,0</t>
+          <t>-2,24; 0,0</t>
         </is>
       </c>
     </row>
@@ -1255,12 +1255,12 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-7,35; 0,0</t>
+          <t>-6,96; 0,0</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-2,82; 7,91</t>
+          <t>-2,96; 8,11</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -1275,12 +1275,12 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-3,82; 0,0</t>
+          <t>-3,92; 0,0</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-1,43; 3,78</t>
+          <t>-1,44; 3,95</t>
         </is>
       </c>
     </row>
@@ -1363,7 +1363,7 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1421,7 +1421,7 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,89</t>
+          <t>0,0; 5,85</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,96</t>
+          <t>0,0; 2,97</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -1519,7 +1519,7 @@
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
@@ -1567,7 +1567,7 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,76</t>
+          <t>0,0; 2,85</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -1577,7 +1577,7 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,45</t>
+          <t>0,0; 2,14</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
@@ -1587,12 +1587,12 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,51</t>
+          <t>0,0; 1,61</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,12</t>
+          <t>0,0; 1,42</t>
         </is>
       </c>
     </row>
@@ -1723,12 +1723,12 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-1,24; 1,19</t>
+          <t>-1,23; 0,81</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-1,91; 0,0</t>
+          <t>-2,06; 0,0</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
@@ -1743,7 +1743,7 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-0,6; 0,59</t>
+          <t>-0,6; 0,58</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
@@ -1879,17 +1879,17 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-0,26; 0,6</t>
+          <t>-0,27; 0,6</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-0,27; 0,52</t>
+          <t>-0,29; 0,52</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-0,11; 0,54</t>
+          <t>-0,1; 0,61</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
@@ -1975,7 +1975,7 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-79,12; 779,25</t>
+          <t>-69,36; 1067,2</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">

--- a/data/trans_camb/IP1013-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/IP1013-Provincia-trans_camb.xlsx
@@ -943,7 +943,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,4</t>
+          <t>0,0; 4,83</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,46</t>
+          <t>0,0; 2,82</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1109,22 +1109,22 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-2,58; 1,67</t>
+          <t>-3,42; 1,65</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-4,27; 0,0</t>
+          <t>-4,23; 0,0</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-1,73; 0,85</t>
+          <t>-1,32; 0,84</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-2,24; 0,0</t>
+          <t>-2,18; 0,0</t>
         </is>
       </c>
     </row>
@@ -1255,12 +1255,12 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-6,96; 0,0</t>
+          <t>-8,34; 0,0</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-2,96; 8,11</t>
+          <t>-2,99; 7,91</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -1275,12 +1275,12 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-3,92; 0,0</t>
+          <t>-3,6; 0,0</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-1,44; 3,95</t>
+          <t>-1,44; 3,88</t>
         </is>
       </c>
     </row>
@@ -1421,7 +1421,7 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,85</t>
+          <t>0,0; 5,83</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,97</t>
+          <t>0,0; 2,99</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -1567,17 +1567,17 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,85</t>
+          <t>0,0; 2,61</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,56</t>
+          <t>0,0; 2,75</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,14</t>
+          <t>0,0; 2,29</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
@@ -1587,12 +1587,12 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,61</t>
+          <t>0,0; 1,71</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,42</t>
+          <t>0,0; 1,26</t>
         </is>
       </c>
     </row>
@@ -1723,12 +1723,12 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-1,23; 0,81</t>
+          <t>-1,24; 0,81</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-2,06; 0,0</t>
+          <t>-2,23; 0,0</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
@@ -1743,7 +1743,7 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-0,6; 0,58</t>
+          <t>-0,79; 0,4</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
@@ -1884,27 +1884,27 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-0,29; 0,52</t>
+          <t>-0,27; 0,56</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-0,1; 0,61</t>
+          <t>-0,1; 0,54</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-0,47; 0,0</t>
+          <t>-0,56; 0,0</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-0,1; 0,43</t>
+          <t>-0,09; 0,43</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-0,23; 0,24</t>
+          <t>-0,22; 0,25</t>
         </is>
       </c>
     </row>
@@ -1975,7 +1975,7 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-69,36; 1067,2</t>
+          <t>-66,5; inf</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">

--- a/data/trans_camb/IP1013-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/IP1013-Provincia-trans_camb.xlsx
@@ -519,13 +519,13 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="F1" s="3" t="n"/>
@@ -905,17 +905,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
           <t>1,07</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -943,7 +943,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,83</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -953,7 +953,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 5,42</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,82</t>
+          <t>0,0; 2,65</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -981,17 +981,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
           <t>inf%</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1061,22 +1061,22 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>-0,04</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>-0,85</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-0,04</t>
+          <t>0,0</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>-0,85</t>
+          <t>0,0</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1099,27 +1099,27 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-2,6; 1,72</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-4,61; 0,0</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-3,42; 1,65</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-4,23; 0,0</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-1,32; 0,84</t>
+          <t>-1,32; 0,86</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1137,22 +1137,22 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>-4,51%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>-100,0%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>-4,51%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>-100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1217,22 +1217,22 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
           <t>-1,49</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="F20" s="2" t="inlineStr">
         <is>
           <t>1,66</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-8,34; 0,0</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-2,99; 7,91</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-7,35; 0,0</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-2,82; 7,91</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-3,6; 0,0</t>
+          <t>-3,82; 0,0</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-1,44; 3,88</t>
+          <t>-1,43; 3,78</t>
         </is>
       </c>
     </row>
@@ -1293,22 +1293,22 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
           <t>-100,0%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="F22" s="2" t="inlineStr">
         <is>
           <t>111,85%</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -1373,7 +1373,7 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>1,14</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1,14</t>
+          <t>0,0</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1411,7 +1411,7 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 5,89</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -1421,7 +1421,7 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,83</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,99</t>
+          <t>0,0; 2,96</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -1449,7 +1449,7 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>inf%</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -1459,7 +1459,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>inf%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1529,22 +1529,22 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>0,43</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
           <t>0,49</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="F28" s="2" t="inlineStr">
         <is>
           <t>0,51</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>0,43</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -1567,32 +1567,32 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,61</t>
+          <t>0,0; 2,45</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,75</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,29</t>
+          <t>0,0; 2,76</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 2,56</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,71</t>
+          <t>0,0; 1,51</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,26</t>
+          <t>0,0; 1,12</t>
         </is>
       </c>
     </row>
@@ -1610,17 +1610,17 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
           <t>inf%</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="F30" s="2" t="inlineStr">
         <is>
           <t>inf%</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -1685,22 +1685,22 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
           <t>-0,01</t>
         </is>
       </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="F32" s="2" t="inlineStr">
         <is>
           <t>-0,41</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -1723,27 +1723,27 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-1,24; 0,81</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-2,23; 0,0</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-1,24; 1,19</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-1,91; 0,0</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-0,79; 0,4</t>
+          <t>-0,6; 0,59</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
@@ -1761,22 +1761,22 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
           <t>-1,3%</t>
         </is>
       </c>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="F34" s="2" t="inlineStr">
         <is>
           <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -1841,22 +1841,22 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
+          <t>0,17</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>-0,09</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
           <t>0,11</t>
         </is>
       </c>
-      <c r="D36" s="2" t="inlineStr">
+      <c r="F36" s="2" t="inlineStr">
         <is>
           <t>0,11</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>0,17</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>-0,09</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -1879,32 +1879,32 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-0,27; 0,6</t>
+          <t>-0,11; 0,54</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-0,27; 0,56</t>
+          <t>-0,47; 0,0</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-0,1; 0,54</t>
+          <t>-0,26; 0,6</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-0,56; 0,0</t>
+          <t>-0,27; 0,52</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-0,09; 0,43</t>
+          <t>-0,1; 0,43</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-0,22; 0,25</t>
+          <t>-0,23; 0,24</t>
         </is>
       </c>
     </row>
@@ -1917,22 +1917,22 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
+          <t>183,98%</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
           <t>58,24%</t>
         </is>
       </c>
-      <c r="D38" s="2" t="inlineStr">
+      <c r="F38" s="2" t="inlineStr">
         <is>
           <t>58,61%</t>
-        </is>
-      </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>183,98%</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -1975,7 +1975,7 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-66,5; inf</t>
+          <t>-79,12; 779,25</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
